--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,10 +461,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>14892</t>
-        </is>
+      <c r="A2" t="n">
+        <v>14892</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -487,6 +485,34 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>100tジェットローダー</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_20260308195408.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-03-08 19:54:13</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,10 +487,8 @@
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>836</t>
-        </is>
+      <c r="A3" t="n">
+        <v>836</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -513,6 +511,34 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>100t移動式チラー</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_20260308195713.jpg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-03-08 19:57:18</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,10 +513,8 @@
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2300</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -539,6 +537,34 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100t温調機</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260308200343.jpg</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-03-08 20:03:50</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>14892</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100tベルトコンベア</t>
+          <t>100t温調機</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,95 +478,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260308195105.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260309113825.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-08 19:51:11</t>
+          <t>2026-03-09 11:38:31</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>836</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>100tジェットローダー</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>200V</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_20260308195408.jpg</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-03-08 19:54:13</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2300</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>100t移動式チラー</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>200V</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_20260308195713.jpg</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-03-08 19:57:18</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>100t温調機</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>200V</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260308200343.jpg</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-03-08 20:03:50</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100t温調機</t>
+          <t>100t金型温度調節器</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,12 +478,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260309113825.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260309114026.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-09 11:38:31</t>
+          <t>2026-03-09 11:40:32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100t金型温度調節器</t>
+          <t>100t金型温度調節機</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,12 +478,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260309114026.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260309114152.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-09 11:40:32</t>
+          <t>2026-03-09 11:42:01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,10 +461,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
+      <c r="A2" t="n">
+        <v>147</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -487,6 +485,34 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2699</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5t金型反転機</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260309114801.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:48:06</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,10 +487,8 @@
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2699</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2699</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -513,6 +511,34 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>14882</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>160tジェットローダー</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14882_20260309125430.jpg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-03-09 12:54:37</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,10 +513,8 @@
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>14882</t>
-        </is>
+      <c r="A4" t="n">
+        <v>14882</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -539,6 +537,34 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>160tベルトコンベア</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>100V</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_20260309134154.jpg</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:42:01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,10 +539,8 @@
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
+      <c r="A5" t="n">
+        <v>197</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -565,6 +563,34 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>160t金型温度調節機</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260309135111.jpg</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:51:16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>147</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100t金型温度調節機</t>
+          <t>160t金型温度調節機</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,121 +478,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260309114152.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260309144534.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-09 11:42:01</t>
+          <t>2026-03-09 14:45:40</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2699</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>5t金型反転機</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>200V</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260309114801.jpg</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-03-09 11:48:06</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>14882</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>160tジェットローダー</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>200V</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14882_20260309125430.jpg</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-03-09 12:54:37</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>197</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>160tベルトコンベア</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>100V</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_20260309134154.jpg</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-03-09 13:42:01</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>160t金型温度調節機</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>200V</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260309135111.jpg</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-03-09 13:51:16</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -478,12 +478,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260309144534.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260310115743.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-09 14:45:40</t>
+          <t>2026-03-10 11:57:51</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,10 +461,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1305</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -487,6 +485,34 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>160HR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>160tHR温度コントローラー</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/160HR_20260310120321.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:03:29</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1305</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>14892</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>160t金型温度調節機</t>
+          <t>100tベルトコンベア</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,43 +478,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260310115743.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260310132241.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-10 11:57:51</t>
+          <t>2026-03-10 13:22:49</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>160HR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>160tHR温度コントローラー</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>200V</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/160HR_20260310120321.jpg</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-03-10 12:03:29</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -478,12 +478,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260310132241.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260310134154.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-10 13:22:49</t>
+          <t>2026-03-10 13:41:58</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -478,12 +478,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260310134154.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260310134229.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-10 13:41:58</t>
+          <t>2026-03-10 13:42:32</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -478,12 +478,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260310134229.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260310134415.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-10 13:42:32</t>
+          <t>2026-03-10 13:44:17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,10 +461,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>14892</t>
-        </is>
+      <c r="A2" t="n">
+        <v>14892</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -487,6 +485,34 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2699</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5t金型反転機</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260310140220.jpg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-03-10 14:02:23</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260310140220.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260310140338.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-10 14:02:23</t>
+          <t>2026-03-10 14:03:42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260310140338.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260310140440.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-10 14:03:42</t>
+          <t>2026-03-10 14:04:46</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260310140440.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-10 14:04:46</t>
+          <t>2026-03-11 08:20:23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 08:20:23</t>
+          <t>2026-03-11 09:27:28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 09:27:28</t>
+          <t>2026-03-11 09:31:34</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 09:31:34</t>
+          <t>2026-03-11 09:40:07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 09:40:07</t>
+          <t>2026-03-11 09:40:47</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311095407.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 09:40:47</t>
+          <t>2026-03-11 09:54:09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311095407.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311095801.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 09:54:09</t>
+          <t>2026-03-11 09:58:03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311095801.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311095841.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 09:58:03</t>
+          <t>2026-03-11 09:58:43</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -462,11 +462,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14892</v>
+        <v>2699</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100tベルトコンベア</t>
+          <t>5t金型反転機</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,12 +476,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260310134415.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311095841.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-10 13:44:17</t>
+          <t>2026-03-11 09:58:43</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -489,12 +489,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5t金型反転機</t>
+          <t>100tベルトコンベア</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311095841.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311105306.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 09:58:43</t>
+          <t>2026-03-11 10:53:11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311105306.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311110141.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 10:53:11</t>
+          <t>2026-03-11 11:01:44</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -462,11 +462,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2699</v>
+        <v>14892</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5t金型反転機</t>
+          <t>100tベルトコンベア</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,12 +476,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311095841.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311110141.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-11 09:58:43</t>
+          <t>2026-03-11 11:01:44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -489,12 +489,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100tベルトコンベア</t>
+          <t>5t金型反転機</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311110141.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311110554.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:01:44</t>
+          <t>2026-03-11 11:05:56</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -462,11 +462,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14892</v>
+        <v>2699</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100tベルトコンベア</t>
+          <t>5t金型反転機</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,12 +476,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311110141.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311110554.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-11 11:01:44</t>
+          <t>2026-03-11 11:05:56</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -489,12 +489,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5t金型反転機</t>
+          <t>100tベルトコンベア</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311110554.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311110930.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:05:56</t>
+          <t>2026-03-11 11:09:34</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311110930.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311111023.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:09:34</t>
+          <t>2026-03-11 11:10:27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311111023.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311113520.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:10:27</t>
+          <t>2026-03-11 11:35:24</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -462,11 +462,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2699</v>
+        <v>14892</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5t金型反転機</t>
+          <t>100tベルトコンベア</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,12 +476,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311110554.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311113520.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-11 11:05:56</t>
+          <t>2026-03-11 11:35:24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -489,12 +489,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100tベルトコンベア</t>
+          <t>5t金型反転機</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311113520.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311113616.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:35:24</t>
+          <t>2026-03-11 11:36:18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311113616.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311115136.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:36:18</t>
+          <t>2026-03-11 11:51:38</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -462,11 +462,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14892</v>
+        <v>2699</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100tベルトコンベア</t>
+          <t>5t金型反転機</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,12 +476,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311113520.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311115136.jpg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-11 11:35:24</t>
+          <t>2026-03-11 11:51:38</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -489,12 +489,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5t金型反転機</t>
+          <t>100tベルトコンベア</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311115136.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311115244.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:51:38</t>
+          <t>2026-03-11 11:52:46</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -504,12 +504,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311115244.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311115306.jpg</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-11 11:52:46</t>
+          <t>2026-03-11 11:53:08</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,10 +487,8 @@
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>14892</t>
-        </is>
+      <c r="A3" t="n">
+        <v>14892</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -513,6 +511,34 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>100tジェットローダー</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_20260311130840.jpg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:08:46</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,10 +513,8 @@
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>836</t>
-        </is>
+      <c r="A4" t="n">
+        <v>836</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -539,6 +537,34 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100t金型温度調整機</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260311131301.jpg</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:13:07</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,27 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <color rgb="000000FF"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +69,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,148 +454,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="115" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>機器台帳マスター</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1"/>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>管理番号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>機器名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>使用電源</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>マニュアルURL</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>機器情報ページURL</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>最終更新日時</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>メモ・備考</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>2699</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>5t金型反転機</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>200V</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311115136.jpg</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>2026-03-11 11:51:38</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>14892</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>100tベルトコンベア</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>200V</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311115306.jpg</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>2026-03-11 11:53:08</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>836</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>100tジェットローダー</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>200V</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_20260311130840.jpg</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-03-11 13:08:46</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>100t金型温度調整機</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>200V</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260311131301.jpg</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-03-11 13:13:07</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>100t移動式チラー</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_20260311140127.jpg</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 14:01:32</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -610,10 +610,8 @@
       <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
+      <c r="A8" s="3" t="n">
+        <v>2300</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -636,6 +634,34 @@
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>160tベルトコンベア</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>100V</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_20260311140540.jpg</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 14:05:46</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -647,6 +673,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -636,10 +636,8 @@
       <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
+      <c r="A9" s="3" t="n">
+        <v>197</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -662,6 +660,34 @@
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>160tジェットローダー</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1488_20260311141138.jpg</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 14:11:45</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -674,6 +700,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -662,10 +662,8 @@
       <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>1488</t>
-        </is>
+      <c r="A10" s="3" t="n">
+        <v>1488</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -688,6 +686,34 @@
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>160t金型温度調節機</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260311141956.jpg</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 14:20:03</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -701,6 +727,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -585,11 +585,11 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>147</v>
+        <v>2300</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>100t金型温度調整機</t>
+          <t>100t移動式チラー</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -599,75 +599,75 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260311131301.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_20260311140127.jpg</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 13:13:07</t>
+          <t>2026-03-11 14:01:32</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>2300</v>
+        <v>197</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>100t移動式チラー</t>
+          <t>160tベルトコンベア</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>200V</t>
+          <t>100V</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_20260311140127.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_20260311140540.jpg</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:01:32</t>
+          <t>2026-03-11 14:05:46</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>197</v>
+        <v>1488</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>160tベルトコンベア</t>
+          <t>160tジェットローダー</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>100V</t>
+          <t>200V</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_20260311140540.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1488_20260311141138.jpg</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:05:46</t>
+          <t>2026-03-11 14:11:45</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>1488</v>
+        <v>1305</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>160tジェットローダー</t>
+          <t>160t金型温度調節機</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1488_20260311141138.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260311141956.jpg</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:11:45</t>
+          <t>2026-03-11 14:20:03</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr"/>
@@ -690,12 +690,12 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>160t金型温度調節機</t>
+          <t>100t金型温度調節機</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260311141956.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260311142200.jpg</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:20:03</t>
+          <t>2026-03-11 14:22:03</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -533,11 +533,11 @@
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>14892</v>
+        <v>836</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>100tベルトコンベア</t>
+          <t>100tジェットローダー</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -547,23 +547,23 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311115306.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_20260311130840.jpg</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 11:53:08</t>
+          <t>2026-03-11 13:08:46</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>836</v>
+        <v>2300</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>100tジェットローダー</t>
+          <t>100t移動式チラー</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -573,75 +573,75 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_20260311130840.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_20260311140127.jpg</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 13:08:46</t>
+          <t>2026-03-11 14:01:32</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>2300</v>
+        <v>197</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>100t移動式チラー</t>
+          <t>160tベルトコンベア</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>200V</t>
+          <t>100V</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_20260311140127.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_20260311140540.jpg</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:01:32</t>
+          <t>2026-03-11 14:05:46</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>197</v>
+        <v>1488</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>160tベルトコンベア</t>
+          <t>160tジェットローダー</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>100V</t>
+          <t>200V</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_20260311140540.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1488_20260311141138.jpg</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:05:46</t>
+          <t>2026-03-11 14:11:45</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>1488</v>
+        <v>1305</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>160tジェットローダー</t>
+          <t>160t金型温度調節機</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -651,23 +651,23 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1488_20260311141138.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260311141956.jpg</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:11:45</t>
+          <t>2026-03-11 14:20:03</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>1305</v>
+        <v>147</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>160t金型温度調節機</t>
+          <t>100t金型温度調節機</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260311141956.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260311142200.jpg</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:20:03</t>
+          <t>2026-03-11 14:22:03</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr"/>
@@ -690,12 +690,12 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>100t金型温度調節機</t>
+          <t>100tベルトコンベア</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260311142200.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311145428.jpg</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:22:03</t>
+          <t>2026-03-11 14:54:32</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -688,10 +688,8 @@
       <c r="F10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>14892</t>
-        </is>
+      <c r="A11" s="3" t="n">
+        <v>14892</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
@@ -714,6 +712,34 @@
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>160HR</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>160tHR温度コントローラー</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/160HR_20260311150154.jpg</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:02:00</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -728,6 +754,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -506,8 +506,10 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="n">
-        <v>2699</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2699</t>
+        </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -532,8 +534,10 @@
       <c r="F4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>836</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -558,8 +562,10 @@
       <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="3" t="n">
-        <v>2300</v>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -584,8 +590,10 @@
       <c r="F6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>197</v>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -610,8 +618,10 @@
       <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="3" t="n">
-        <v>1488</v>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
@@ -636,8 +646,10 @@
       <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>1305</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
@@ -662,8 +674,10 @@
       <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="n">
-        <v>147</v>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -688,8 +702,10 @@
       <c r="F10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>14892</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>14892</t>
+        </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
@@ -740,6 +756,34 @@
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2401</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>220tベルトコンベア</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>100V</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2401_20260311150654.jpg</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:07:03</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -755,6 +799,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -775,12 +775,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2401_20260311150654.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2401_20260311151611.jpg</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:07:03</t>
+          <t>2026-03-11 15:16:17</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -784,6 +784,34 @@
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>220tジェットローダー</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1314_20260311152217.jpg</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:22:23</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -800,6 +828,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -812,6 +812,34 @@
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>220t金型温度調節機</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/192_20260311152535.jpg</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:25:41</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -829,6 +857,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -840,6 +840,34 @@
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>220t移動式チラー</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2302_20260311152737.jpg</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:27:43</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -858,6 +886,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -868,6 +868,34 @@
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>220HR</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>220tHR温度コントローラー</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/220HR_20260311153023.jpg</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:30:28</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -887,6 +915,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -896,6 +896,34 @@
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>450tベルトコンベア</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2109_20260311153309.jpg</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:33:16</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -916,6 +944,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -924,6 +924,34 @@
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>450tジェットローダー</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/835_20260311153538.jpg</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:35:43</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -945,6 +973,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -952,6 +952,34 @@
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>550tベルトコンベア</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_20260311153750.jpg</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:37:56</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -974,6 +1002,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -980,6 +980,34 @@
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>4891</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>550tジェットローダー</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/4891_20260311153928.jpg</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:39:34</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1003,6 +1031,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1008,6 +1008,34 @@
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2206</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>二室式箱型乾燥機</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>200V</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2206_20260311154206.jpg</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:42:11</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1032,6 +1060,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="機器台帳マスター" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'機器台帳マスター'!$A$3:$F$22</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -508,12 +510,12 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>5t金型反転機</t>
+          <t>100t金型温度調節機</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -523,12 +525,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_20260311115136.jpg</t>
+          <t>http://192.168.11.8:8000/147_2149.jpg</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 11:51:38</t>
+          <t>2026-03-14 21:49:51</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr"/>
@@ -536,12 +538,12 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>160HR</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>100tジェットローダー</t>
+          <t>160tHR温度コントローラー</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -551,12 +553,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_20260311130840.jpg</t>
+          <t>http://192.168.11.8:8000/160HR_1843.jpg</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 13:08:46</t>
+          <t>2026-03-14 18:43:26</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>
@@ -564,12 +566,12 @@
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>192</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>100t移動式チラー</t>
+          <t>220t金型温度調節機</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -579,12 +581,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_20260311140127.jpg</t>
+          <t>http://192.168.11.8:8000/192_2135.jpg</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:01:32</t>
+          <t>2026-03-14 21:35:10</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
@@ -607,12 +609,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_20260311140540.jpg</t>
+          <t>http://192.168.11.8:8000/197_2218.jpg</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:05:46</t>
+          <t>2026-03-14 22:18:45</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr"/>
@@ -620,12 +622,12 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>220HR</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>160tジェットローダー</t>
+          <t>220tHR温度コントローラー</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -635,12 +637,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1488_20260311141138.jpg</t>
+          <t>http://192.168.11.8:8000/220HR_2137.jpg</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:11:45</t>
+          <t>2026-03-14 21:37:22</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
@@ -648,12 +650,12 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>835</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>160t金型温度調節機</t>
+          <t>450tジェットローダー</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -663,12 +665,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_20260311141956.jpg</t>
+          <t>http://192.168.11.8:8000/835_2137.jpg</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:20:03</t>
+          <t>2026-03-14 21:37:49</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -676,12 +678,12 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>836</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>100t金型温度調節機</t>
+          <t>100tジェットローダー</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -691,12 +693,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_20260311142200.jpg</t>
+          <t>http://192.168.11.8:8000/836_2217.jpg</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:22:03</t>
+          <t>2026-03-14 22:17:50</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr"/>
@@ -704,12 +706,12 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>14892</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>100tベルトコンベア</t>
+          <t>160t金型温度調節機</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -719,12 +721,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_20260311145428.jpg</t>
+          <t>http://192.168.11.8:8000/1305_2139.jpg</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 14:54:32</t>
+          <t>2026-03-14 21:39:16</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
@@ -732,12 +734,12 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>160HR</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>160tHR温度コントローラー</t>
+          <t>220tジェットローダー</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -747,12 +749,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/160HR_20260311150154.jpg</t>
+          <t>http://192.168.11.8:8000/1314_2114.jpg</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:02:00</t>
+          <t>2026-03-14 21:14:45</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr"/>
@@ -760,27 +762,27 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>220tベルトコンベア</t>
+          <t>160tジェットローダー</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>100V</t>
+          <t>200V</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2401_20260311151611.jpg</t>
+          <t>http://192.168.11.8:8000/1488_2219.jpg</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:16:17</t>
+          <t>2026-03-14 22:19:27</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -788,12 +790,12 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>220tジェットローダー</t>
+          <t>450tベルトコンベア</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -803,12 +805,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1314_20260311152217.jpg</t>
+          <t>http://192.168.11.8:8000/2109_2210.jpg</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:22:23</t>
+          <t>2026-03-14 22:10:52</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
@@ -816,12 +818,12 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>220t金型温度調節機</t>
+          <t>二室式箱型乾燥機</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -831,12 +833,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/192_20260311152535.jpg</t>
+          <t>http://192.168.11.8:8000/2206_2142.jpg</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:25:41</t>
+          <t>2026-03-14 21:42:52</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -844,12 +846,12 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>220t移動式チラー</t>
+          <t>100t移動式チラー</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -859,12 +861,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2302_20260311152737.jpg</t>
+          <t>http://192.168.11.8:8000/2300_2220.jpg</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:27:43</t>
+          <t>2026-03-14 22:20:08</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -872,12 +874,12 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>220HR</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>220tHR温度コントローラー</t>
+          <t>220t移動式チラー</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -887,12 +889,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/220HR_20260311153023.jpg</t>
+          <t>http://192.168.11.8:8000/2302_2214.jpg</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:30:28</t>
+          <t>2026-03-14 22:14:49</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -900,12 +902,12 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>450tベルトコンベア</t>
+          <t>550tベルトコンベア</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -915,12 +917,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2109_20260311153309.jpg</t>
+          <t>http://192.168.11.8:8000/2400_2216.jpg</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:33:16</t>
+          <t>2026-03-14 22:16:20</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
@@ -928,27 +930,27 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>450tジェットローダー</t>
+          <t>220tベルトコンベア</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>200V</t>
+          <t>100V</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/835_20260311153538.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2401_1413.jpg</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:35:43</t>
+          <t>2026-03-15 14:13:14</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
@@ -956,12 +958,12 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>550tベルトコンベア</t>
+          <t>5t金型反転機</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -971,12 +973,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_20260311153750.jpg</t>
+          <t>http://192.168.11.8:8000/2699_2217.jpg</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:37:56</t>
+          <t>2026-03-14 22:17:18</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
@@ -999,12 +1001,12 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/4891_20260311153928.jpg</t>
+          <t>http://192.168.11.8:8000/4891_2150.jpg</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:39:34</t>
+          <t>2026-03-14 21:50:45</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
@@ -1012,12 +1014,12 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>二室式箱型乾燥機</t>
+          <t>100tベルトコンベア</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1027,17 +1029,18 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2206_20260311154206.jpg</t>
+          <t>http://192.168.11.8:8000/14892_2138.jpg</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-11 15:42:11</t>
+          <t>2026-03-14 21:38:44</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:F22"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F2"/>
   </mergeCells>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -945,12 +945,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2401_1413.jpg</t>
+          <t>http://192.168.11.8:8000/2401_1912.jpg</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-03-15 14:13:14</t>
+          <t>2026-03-14 19:12:58</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/14892_2138.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_2337.jpg</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:38:44</t>
+          <t>2026-03-25 23:37:11</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -1029,12 +1029,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_2337.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_2339.jpg</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:37:11</t>
+          <t>2026-03-25 23:39:23</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -609,12 +609,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/197_2218.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_2341.jpg</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:18:45</t>
+          <t>2026-03-25 23:41:09</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/1305_2139.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_2342.jpg</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:39:16</t>
+          <t>2026-03-25 23:42:21</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/192_2135.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/192_2343.jpg</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:35:10</t>
+          <t>2026-03-25 23:43:16</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/147_2149.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_2344.jpg</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:49:51</t>
+          <t>2026-03-25 23:44:19</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -553,12 +553,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/160HR_1843.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/160HR_2345.jpg</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 18:43:26</t>
+          <t>2026-03-25 23:45:34</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -945,12 +945,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2401_1912.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2401_2346.jpg</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 19:12:58</t>
+          <t>2026-03-25 23:46:28</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -749,12 +749,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/1314_2114.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1314_2347.jpg</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:14:45</t>
+          <t>2026-03-25 23:47:11</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -637,12 +637,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/220HR_2137.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/220HR_2347.jpg</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:37:22</t>
+          <t>2026-03-25 23:47:59</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -805,12 +805,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2109_2210.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2109_2348.jpg</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:10:52</t>
+          <t>2026-03-25 23:48:49</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -665,12 +665,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/835_2137.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/835_2349.jpg</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:37:49</t>
+          <t>2026-03-25 23:49:32</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -1001,12 +1001,12 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/4891_2150.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/4891_2350.jpg</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:50:45</t>
+          <t>2026-03-25 23:50:18</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -889,12 +889,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2302_2214.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2302_2351.jpg</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:14:49</t>
+          <t>2026-03-25 23:51:32</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -917,12 +917,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2400_2216.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_2352.jpg</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:16:20</t>
+          <t>2026-03-25 23:52:14</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/836_2217.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_2352.jpg</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:17:50</t>
+          <t>2026-03-25 23:53:01</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/1488_2219.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1488_2353.jpg</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:19:27</t>
+          <t>2026-03-25 23:53:52</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -861,12 +861,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2300_2220.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_2354.jpg</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:20:08</t>
+          <t>2026-03-25 23:54:34</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -912,17 +912,17 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>200V</t>
+          <t>100V</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_2352.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_0518.jpg</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:52:14</t>
+          <t>2026-03-26 05:18:16</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -833,12 +833,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2206_2142.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2206_0519.jpg</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:42:52</t>
+          <t>2026-03-26 05:19:11</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -973,12 +973,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2699_2217.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_0520.jpg</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:17:18</t>
+          <t>2026-03-26 05:20:45</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_2344.jpg</t>
+          <t>http://192.168.11.8:8000/147_2149.jpg</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:44:19</t>
+          <t>2026-03-14 21:49:51</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr"/>
@@ -553,12 +553,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/160HR_2345.jpg</t>
+          <t>http://192.168.11.8:8000/160HR_1843.jpg</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:45:34</t>
+          <t>2026-03-14 18:43:26</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/192_2343.jpg</t>
+          <t>http://192.168.11.8:8000/192_2135.jpg</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:43:16</t>
+          <t>2026-03-14 21:35:10</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
@@ -609,12 +609,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_2341.jpg</t>
+          <t>http://192.168.11.8:8000/197_2218.jpg</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:41:09</t>
+          <t>2026-03-14 22:18:45</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr"/>
@@ -637,12 +637,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/220HR_2347.jpg</t>
+          <t>http://192.168.11.8:8000/220HR_2137.jpg</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:47:59</t>
+          <t>2026-03-14 21:37:22</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
@@ -665,12 +665,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/835_2349.jpg</t>
+          <t>http://192.168.11.8:8000/835_2137.jpg</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:49:32</t>
+          <t>2026-03-14 21:37:49</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -693,12 +693,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_2352.jpg</t>
+          <t>http://192.168.11.8:8000/836_2217.jpg</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:53:01</t>
+          <t>2026-03-14 22:17:50</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr"/>
@@ -721,12 +721,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_2342.jpg</t>
+          <t>http://192.168.11.8:8000/1305_2139.jpg</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:42:21</t>
+          <t>2026-03-14 21:39:16</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
@@ -749,12 +749,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1314_2347.jpg</t>
+          <t>http://192.168.11.8:8000/1314_2114.jpg</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:47:11</t>
+          <t>2026-03-14 21:14:45</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr"/>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1488_2353.jpg</t>
+          <t>http://192.168.11.8:8000/1488_2219.jpg</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:53:52</t>
+          <t>2026-03-14 22:19:27</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -805,12 +805,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2109_2348.jpg</t>
+          <t>http://192.168.11.8:8000/2109_2210.jpg</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:48:49</t>
+          <t>2026-03-14 22:10:52</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
@@ -833,12 +833,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2206_0519.jpg</t>
+          <t>http://192.168.11.8:8000/2206_2142.jpg</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-03-26 05:19:11</t>
+          <t>2026-03-14 21:42:52</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -861,12 +861,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_2354.jpg</t>
+          <t>http://192.168.11.8:8000/2300_2220.jpg</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:54:34</t>
+          <t>2026-03-14 22:20:08</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -889,12 +889,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2302_2351.jpg</t>
+          <t>http://192.168.11.8:8000/2302_2214.jpg</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:51:32</t>
+          <t>2026-03-14 22:14:49</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -912,17 +912,17 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>100V</t>
+          <t>200V</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_0518.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_2345.jpg</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-26 05:18:16</t>
+          <t>2026-03-26 23:45:41</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
@@ -945,12 +945,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2401_2346.jpg</t>
+          <t>http://192.168.11.8:8000/2401_1912.jpg</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:46:28</t>
+          <t>2026-03-14 19:12:58</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_0520.jpg</t>
+          <t>http://192.168.11.8:8000/2699_2217.jpg</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-26 05:20:45</t>
+          <t>2026-03-14 22:17:18</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/4891_2350.jpg</t>
+          <t>http://192.168.11.8:8000/4891_2150.jpg</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:50:18</t>
+          <t>2026-03-14 21:50:45</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_2339.jpg</t>
+          <t>http://192.168.11.8:8000/14892_0518.jpg</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-25 23:39:23</t>
+          <t>2026-03-24 05:18:27</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -917,12 +917,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_2345.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_2353.jpg</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-26 23:45:41</t>
+          <t>2026-03-26 23:53:58</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/147_2149.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/147_2344.jpg</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:49:51</t>
+          <t>2026-03-25 23:44:19</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr"/>
@@ -553,12 +553,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/160HR_1843.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/160HR_2345.jpg</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 18:43:26</t>
+          <t>2026-03-25 23:45:34</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/192_2135.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/192_2343.jpg</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:35:10</t>
+          <t>2026-03-25 23:43:16</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr"/>
@@ -609,12 +609,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/197_2218.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/197_2341.jpg</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:18:45</t>
+          <t>2026-03-25 23:41:09</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr"/>
@@ -637,12 +637,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/220HR_2137.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/220HR_2347.jpg</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:37:22</t>
+          <t>2026-03-25 23:47:59</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr"/>
@@ -665,12 +665,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/835_2137.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/835_2349.jpg</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:37:49</t>
+          <t>2026-03-25 23:49:32</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr"/>
@@ -693,12 +693,12 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/836_2217.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/836_2352.jpg</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:17:50</t>
+          <t>2026-03-25 23:53:01</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr"/>
@@ -721,12 +721,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/1305_2139.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1305_2342.jpg</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:39:16</t>
+          <t>2026-03-25 23:42:21</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr"/>
@@ -749,12 +749,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/1314_2114.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1314_2347.jpg</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:14:45</t>
+          <t>2026-03-25 23:47:11</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr"/>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/1488_2219.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/1488_2353.jpg</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:19:27</t>
+          <t>2026-03-25 23:53:52</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr"/>
@@ -805,12 +805,12 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2109_2210.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2109_2348.jpg</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:10:52</t>
+          <t>2026-03-25 23:48:49</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
@@ -833,12 +833,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2206_2142.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2206_0519.jpg</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:42:52</t>
+          <t>2026-03-26 05:19:11</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr"/>
@@ -861,12 +861,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2300_2220.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2300_2354.jpg</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:20:08</t>
+          <t>2026-03-25 23:54:34</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
@@ -889,12 +889,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2302_2214.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2302_2351.jpg</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:14:49</t>
+          <t>2026-03-25 23:51:32</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr"/>
@@ -917,12 +917,12 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_2353.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_0103.jpg</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-26 23:53:58</t>
+          <t>2026-03-29 01:03:44</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
@@ -945,12 +945,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2401_1912.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2401_2346.jpg</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 19:12:58</t>
+          <t>2026-03-25 23:46:28</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/2699_2217.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2699_0520.jpg</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 22:17:18</t>
+          <t>2026-03-26 05:20:45</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/4891_2150.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/4891_2350.jpg</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-03-14 21:50:45</t>
+          <t>2026-03-25 23:50:18</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>http://192.168.11.8:8000/14892_0518.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/14892_2339.jpg</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-03-24 05:18:27</t>
+          <t>2026-03-25 23:39:23</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr"/>

--- a/ledger/機器台帳マスター.xlsx
+++ b/ledger/機器台帳マスター.xlsx
@@ -912,17 +912,17 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>200V</t>
+          <t>100V</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_0103.jpg</t>
+          <t>https://cdn.jsdelivr.net/gh/equipment-portal/qr-manager@main/manuals/2400_0104.jpg</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-03-29 01:03:44</t>
+          <t>2026-03-29 01:04:48</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
